--- a/87/food/2026-01-13-sm.xlsx
+++ b/87/food/2026-01-13-sm.xlsx
@@ -838,7 +838,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>МБОУ "Илсхан-Юртовская ОШ"</t>
+          <t>МБОУ «Илсхан-Юртовская ОШ»</t>
         </is>
       </c>
       <c r="C1" s="39" t="n"/>
@@ -857,7 +857,7 @@
       </c>
       <c r="J1" s="11" t="inlineStr">
         <is>
-          <t>13.01.2026</t>
+          <t>2026-01-13</t>
         </is>
       </c>
     </row>
